--- a/DATA/ENGINEER SCHEDULES/Barrett Woodyard & Associates.xlsx
+++ b/DATA/ENGINEER SCHEDULES/Barrett Woodyard & Associates.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ericc\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\HHpro\DATA\ENGINEER SCHEDULES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03BE6BA0-4727-4B53-A1DA-1DA1EC8B4B3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41244E6F-DDC0-46FA-B8DC-3B7F3B883AFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -518,7 +518,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="22">
+  <borders count="23">
     <border>
       <left/>
       <right/>
@@ -769,12 +769,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -790,15 +801,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -814,18 +816,186 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -835,197 +1005,41 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1362,525 +1376,455 @@
   </cols>
   <sheetData>
     <row r="1" spans="3:25" ht="36.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="75" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
-      <c r="N1" s="5"/>
-      <c r="O1" s="5"/>
-      <c r="P1" s="5"/>
-      <c r="Q1" s="5"/>
-      <c r="R1" s="5"/>
-      <c r="S1" s="5"/>
-      <c r="T1" s="5"/>
-      <c r="U1" s="5"/>
-      <c r="V1" s="5"/>
-      <c r="W1" s="5"/>
-      <c r="X1" s="5"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="75"/>
+      <c r="F1" s="75"/>
+      <c r="G1" s="75"/>
+      <c r="H1" s="75"/>
+      <c r="I1" s="75"/>
+      <c r="J1" s="75"/>
+      <c r="K1" s="75"/>
+      <c r="L1" s="75"/>
+      <c r="M1" s="75"/>
+      <c r="N1" s="75"/>
+      <c r="O1" s="75"/>
+      <c r="P1" s="75"/>
+      <c r="Q1" s="75"/>
+      <c r="R1" s="75"/>
+      <c r="S1" s="75"/>
+      <c r="T1" s="75"/>
+      <c r="U1" s="75"/>
+      <c r="V1" s="75"/>
+      <c r="W1" s="75"/>
+      <c r="X1" s="75"/>
       <c r="Y1" s="1"/>
     </row>
     <row r="2" spans="3:25" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="13" t="s">
+      <c r="C2" s="76"/>
+      <c r="D2" s="76"/>
+      <c r="E2" s="76"/>
+      <c r="F2" s="67" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="14"/>
-      <c r="H2" s="14"/>
-      <c r="I2" s="14"/>
-      <c r="J2" s="14"/>
-      <c r="K2" s="14"/>
-      <c r="L2" s="14"/>
-      <c r="M2" s="14"/>
-      <c r="N2" s="15"/>
-      <c r="O2" s="17" t="s">
+      <c r="G2" s="68"/>
+      <c r="H2" s="68"/>
+      <c r="I2" s="68"/>
+      <c r="J2" s="68"/>
+      <c r="K2" s="68"/>
+      <c r="L2" s="68"/>
+      <c r="M2" s="68"/>
+      <c r="N2" s="69"/>
+      <c r="O2" s="70" t="s">
         <v>26</v>
       </c>
-      <c r="P2" s="18"/>
-      <c r="Q2" s="18"/>
-      <c r="R2" s="19"/>
-      <c r="S2" s="7" t="s">
+      <c r="P2" s="71"/>
+      <c r="Q2" s="71"/>
+      <c r="R2" s="72"/>
+      <c r="S2" s="73" t="s">
         <v>1</v>
       </c>
-      <c r="T2" s="7"/>
-      <c r="U2" s="7"/>
-      <c r="V2" s="7"/>
-      <c r="W2" s="8"/>
-      <c r="X2" s="8"/>
+      <c r="T2" s="73"/>
+      <c r="U2" s="73"/>
+      <c r="V2" s="73"/>
+      <c r="W2" s="5"/>
+      <c r="X2" s="5"/>
       <c r="Y2" s="3"/>
     </row>
     <row r="3" spans="3:25" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="76" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="76" t="s">
         <v>22</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="76" t="s">
         <v>23</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H3" s="76" t="s">
         <v>46</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="I3" s="73" t="s">
         <v>24</v>
       </c>
-      <c r="J3" s="9" t="s">
+      <c r="J3" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="K3" s="9" t="s">
+      <c r="K3" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="L3" s="7" t="s">
+      <c r="L3" s="73" t="s">
         <v>4</v>
       </c>
-      <c r="M3" s="7" t="s">
+      <c r="M3" s="73" t="s">
         <v>45</v>
       </c>
-      <c r="N3" s="7" t="s">
+      <c r="N3" s="73" t="s">
         <v>5</v>
       </c>
-      <c r="O3" s="17" t="s">
+      <c r="O3" s="70" t="s">
         <v>27</v>
       </c>
-      <c r="P3" s="19"/>
-      <c r="Q3" s="13" t="s">
+      <c r="P3" s="72"/>
+      <c r="Q3" s="67" t="s">
         <v>28</v>
       </c>
-      <c r="R3" s="15"/>
-      <c r="S3" s="7" t="s">
+      <c r="R3" s="69"/>
+      <c r="S3" s="73" t="s">
         <v>30</v>
       </c>
-      <c r="T3" s="7" t="s">
+      <c r="T3" s="73" t="s">
         <v>4</v>
       </c>
-      <c r="U3" s="7" t="s">
+      <c r="U3" s="73" t="s">
         <v>6</v>
       </c>
-      <c r="V3" s="32" t="s">
+      <c r="V3" s="74" t="s">
         <v>40</v>
       </c>
-      <c r="W3" s="7" t="s">
+      <c r="W3" s="73" t="s">
         <v>7</v>
       </c>
-      <c r="X3" s="7" t="s">
+      <c r="X3" s="73" t="s">
         <v>8</v>
       </c>
       <c r="Y3" s="3"/>
     </row>
     <row r="4" spans="3:25" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="9" t="s">
+      <c r="C4" s="76"/>
+      <c r="D4" s="76"/>
+      <c r="E4" s="76"/>
+      <c r="F4" s="76"/>
+      <c r="G4" s="76"/>
+      <c r="H4" s="76"/>
+      <c r="I4" s="73"/>
+      <c r="J4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="K4" s="9" t="s">
+      <c r="K4" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="L4" s="7"/>
-      <c r="M4" s="7"/>
-      <c r="N4" s="7"/>
-      <c r="O4" s="9" t="s">
+      <c r="L4" s="73"/>
+      <c r="M4" s="73"/>
+      <c r="N4" s="73"/>
+      <c r="O4" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="P4" s="9" t="s">
+      <c r="P4" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="Q4" s="9" t="s">
+      <c r="Q4" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="R4" s="9" t="s">
+      <c r="R4" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="S4" s="7"/>
-      <c r="T4" s="7"/>
-      <c r="U4" s="7"/>
-      <c r="V4" s="32"/>
-      <c r="W4" s="7"/>
-      <c r="X4" s="7"/>
+      <c r="S4" s="73"/>
+      <c r="T4" s="73"/>
+      <c r="U4" s="73"/>
+      <c r="V4" s="74"/>
+      <c r="W4" s="73"/>
+      <c r="X4" s="73"/>
       <c r="Y4" s="3"/>
     </row>
     <row r="5" spans="3:25" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="10">
+      <c r="D5" s="7">
         <v>18000</v>
       </c>
-      <c r="E5" s="10">
+      <c r="E5" s="7">
         <v>14040</v>
       </c>
-      <c r="F5" s="11">
+      <c r="F5" s="8">
         <v>620</v>
       </c>
-      <c r="G5" s="11" t="s">
+      <c r="G5" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="H5" s="12">
+      <c r="H5" s="9">
         <v>0.5</v>
       </c>
-      <c r="I5" s="20">
+      <c r="I5" s="11">
         <v>0.75</v>
       </c>
-      <c r="J5" s="11">
+      <c r="J5" s="8">
         <v>80</v>
       </c>
-      <c r="K5" s="11">
+      <c r="K5" s="8">
         <v>67</v>
       </c>
-      <c r="L5" s="16" t="s">
+      <c r="L5" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="M5" s="16" t="s">
+      <c r="M5" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="N5" s="16" t="s">
+      <c r="N5" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="O5" s="16" t="s">
+      <c r="O5" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="P5" s="16" t="s">
+      <c r="P5" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="Q5" s="16" t="s">
+      <c r="Q5" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="R5" s="11">
+      <c r="R5" s="8">
         <v>5</v>
       </c>
-      <c r="S5" s="11">
+      <c r="S5" s="8">
         <v>95</v>
       </c>
-      <c r="T5" s="16" t="s">
+      <c r="T5" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="U5" s="11">
+      <c r="U5" s="8">
         <v>1</v>
       </c>
-      <c r="V5" s="12" t="s">
+      <c r="V5" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="W5" s="16" t="s">
+      <c r="W5" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="X5" s="20" t="s">
+      <c r="X5" s="11" t="s">
         <v>31</v>
       </c>
       <c r="Y5" s="3"/>
     </row>
     <row r="6" spans="3:25" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C6" s="16" t="s">
+      <c r="C6" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="10">
+      <c r="D6" s="7">
         <v>34400</v>
       </c>
-      <c r="E6" s="10">
+      <c r="E6" s="7">
         <v>26144</v>
       </c>
-      <c r="F6" s="11">
+      <c r="F6" s="8">
         <v>1170</v>
       </c>
-      <c r="G6" s="11" t="s">
+      <c r="G6" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="H6" s="12">
+      <c r="H6" s="9">
         <v>0.5</v>
       </c>
-      <c r="I6" s="20">
+      <c r="I6" s="11">
         <v>0.75</v>
       </c>
-      <c r="J6" s="11">
+      <c r="J6" s="8">
         <v>80</v>
       </c>
-      <c r="K6" s="11">
+      <c r="K6" s="8">
         <v>67</v>
       </c>
-      <c r="L6" s="16" t="s">
+      <c r="L6" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="M6" s="16" t="s">
+      <c r="M6" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="N6" s="16" t="s">
+      <c r="N6" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="O6" s="16" t="s">
+      <c r="O6" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="P6" s="16" t="s">
+      <c r="P6" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="Q6" s="16" t="s">
+      <c r="Q6" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="R6" s="11">
+      <c r="R6" s="8">
         <v>8</v>
       </c>
-      <c r="S6" s="11">
+      <c r="S6" s="8">
         <v>95</v>
       </c>
-      <c r="T6" s="16" t="s">
+      <c r="T6" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="U6" s="11">
+      <c r="U6" s="8">
         <v>1</v>
       </c>
-      <c r="V6" s="12" t="s">
+      <c r="V6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="W6" s="16" t="s">
+      <c r="W6" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="X6" s="20" t="s">
+      <c r="X6" s="11" t="s">
         <v>31</v>
       </c>
       <c r="Y6" s="3"/>
     </row>
     <row r="7" spans="3:25" x14ac:dyDescent="0.2">
-      <c r="C7" s="21" t="s">
+      <c r="C7" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="22"/>
-      <c r="E7" s="22"/>
-      <c r="F7" s="22"/>
-      <c r="G7" s="22"/>
-      <c r="H7" s="22"/>
-      <c r="I7" s="22"/>
-      <c r="J7" s="22"/>
-      <c r="K7" s="22"/>
-      <c r="L7" s="22"/>
-      <c r="M7" s="22"/>
-      <c r="N7" s="22"/>
-      <c r="O7" s="22"/>
-      <c r="P7" s="22"/>
-      <c r="Q7" s="22"/>
-      <c r="R7" s="22"/>
-      <c r="S7" s="22"/>
-      <c r="T7" s="22"/>
-      <c r="U7" s="22"/>
-      <c r="V7" s="22"/>
-      <c r="W7" s="22"/>
-      <c r="X7" s="23"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="13"/>
+      <c r="G7" s="13"/>
+      <c r="H7" s="13"/>
+      <c r="I7" s="13"/>
+      <c r="J7" s="13"/>
+      <c r="K7" s="13"/>
+      <c r="L7" s="13"/>
+      <c r="M7" s="13"/>
+      <c r="N7" s="13"/>
+      <c r="O7" s="13"/>
+      <c r="P7" s="13"/>
+      <c r="Q7" s="13"/>
+      <c r="R7" s="13"/>
+      <c r="S7" s="13"/>
+      <c r="T7" s="13"/>
+      <c r="U7" s="13"/>
+      <c r="V7" s="13"/>
+      <c r="W7" s="13"/>
+      <c r="X7" s="14"/>
       <c r="Y7" s="4"/>
     </row>
     <row r="8" spans="3:25" x14ac:dyDescent="0.2">
-      <c r="C8" s="24" t="s">
+      <c r="C8" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="D8" s="25"/>
-      <c r="E8" s="25"/>
-      <c r="F8" s="25"/>
-      <c r="G8" s="25"/>
-      <c r="H8" s="25"/>
-      <c r="I8" s="25"/>
-      <c r="J8" s="25"/>
-      <c r="K8" s="25"/>
-      <c r="L8" s="25"/>
-      <c r="M8" s="25"/>
-      <c r="N8" s="25"/>
-      <c r="O8" s="25"/>
-      <c r="P8" s="25"/>
-      <c r="Q8" s="25"/>
-      <c r="R8" s="25"/>
-      <c r="S8" s="25"/>
-      <c r="T8" s="25"/>
-      <c r="U8" s="25"/>
-      <c r="V8" s="25"/>
-      <c r="W8" s="25"/>
-      <c r="X8" s="26"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="4"/>
+      <c r="M8" s="4"/>
+      <c r="N8" s="4"/>
+      <c r="O8" s="4"/>
+      <c r="P8" s="4"/>
+      <c r="Q8" s="4"/>
+      <c r="R8" s="4"/>
+      <c r="S8" s="4"/>
+      <c r="T8" s="4"/>
+      <c r="U8" s="4"/>
+      <c r="V8" s="4"/>
+      <c r="W8" s="4"/>
+      <c r="X8" s="16"/>
       <c r="Y8" s="4"/>
     </row>
     <row r="9" spans="3:25" x14ac:dyDescent="0.2">
-      <c r="C9" s="24" t="s">
+      <c r="C9" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="D9" s="25"/>
-      <c r="E9" s="25"/>
-      <c r="F9" s="25"/>
-      <c r="G9" s="25"/>
-      <c r="H9" s="25"/>
-      <c r="I9" s="25"/>
-      <c r="J9" s="25"/>
-      <c r="K9" s="25"/>
-      <c r="L9" s="25"/>
-      <c r="M9" s="25"/>
-      <c r="N9" s="25"/>
-      <c r="O9" s="25"/>
-      <c r="P9" s="25"/>
-      <c r="Q9" s="25"/>
-      <c r="R9" s="25"/>
-      <c r="S9" s="25"/>
-      <c r="T9" s="25"/>
-      <c r="U9" s="25"/>
-      <c r="V9" s="25"/>
-      <c r="W9" s="25"/>
-      <c r="X9" s="26"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="K9" s="4"/>
+      <c r="L9" s="4"/>
+      <c r="M9" s="4"/>
+      <c r="N9" s="4"/>
+      <c r="O9" s="4"/>
+      <c r="P9" s="4"/>
+      <c r="Q9" s="4"/>
+      <c r="R9" s="4"/>
+      <c r="S9" s="4"/>
+      <c r="T9" s="4"/>
+      <c r="U9" s="4"/>
+      <c r="V9" s="4"/>
+      <c r="W9" s="4"/>
+      <c r="X9" s="16"/>
       <c r="Y9" s="4"/>
     </row>
     <row r="10" spans="3:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C10" s="24" t="s">
+      <c r="C10" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="D10" s="25"/>
-      <c r="E10" s="25"/>
-      <c r="F10" s="25"/>
-      <c r="G10" s="25"/>
-      <c r="H10" s="25"/>
-      <c r="I10" s="25"/>
-      <c r="J10" s="25"/>
-      <c r="K10" s="25"/>
-      <c r="L10" s="25"/>
-      <c r="M10" s="25"/>
-      <c r="N10" s="25"/>
-      <c r="O10" s="25"/>
-      <c r="P10" s="25"/>
-      <c r="Q10" s="25"/>
-      <c r="R10" s="25"/>
-      <c r="S10" s="25"/>
-      <c r="T10" s="25"/>
-      <c r="U10" s="25"/>
-      <c r="V10" s="25"/>
-      <c r="W10" s="25"/>
-      <c r="X10" s="26"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="K10" s="4"/>
+      <c r="L10" s="4"/>
+      <c r="M10" s="4"/>
+      <c r="N10" s="4"/>
+      <c r="O10" s="4"/>
+      <c r="P10" s="4"/>
+      <c r="Q10" s="4"/>
+      <c r="R10" s="4"/>
+      <c r="S10" s="4"/>
+      <c r="T10" s="4"/>
+      <c r="U10" s="4"/>
+      <c r="V10" s="4"/>
+      <c r="W10" s="4"/>
+      <c r="X10" s="16"/>
       <c r="Y10" s="4"/>
     </row>
     <row r="11" spans="3:25" x14ac:dyDescent="0.2">
-      <c r="C11" s="24" t="s">
+      <c r="C11" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="D11" s="27"/>
-      <c r="E11" s="27"/>
-      <c r="F11" s="27"/>
-      <c r="G11" s="27"/>
-      <c r="H11" s="27"/>
-      <c r="I11" s="27"/>
-      <c r="J11" s="27"/>
-      <c r="K11" s="27"/>
-      <c r="L11" s="27"/>
-      <c r="M11" s="27"/>
-      <c r="N11" s="27"/>
-      <c r="O11" s="27"/>
-      <c r="P11" s="27"/>
-      <c r="Q11" s="27"/>
-      <c r="R11" s="27"/>
-      <c r="S11" s="27"/>
-      <c r="T11" s="27"/>
-      <c r="U11" s="27"/>
-      <c r="V11" s="27"/>
-      <c r="W11" s="27"/>
-      <c r="X11" s="28"/>
+      <c r="X11" s="17"/>
     </row>
     <row r="12" spans="3:25" x14ac:dyDescent="0.2">
-      <c r="C12" s="24" t="s">
+      <c r="C12" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="D12" s="27"/>
-      <c r="E12" s="27"/>
-      <c r="F12" s="27"/>
-      <c r="G12" s="27"/>
-      <c r="H12" s="27"/>
-      <c r="I12" s="27"/>
-      <c r="J12" s="27"/>
-      <c r="K12" s="27"/>
-      <c r="L12" s="27"/>
-      <c r="M12" s="27"/>
-      <c r="N12" s="27"/>
-      <c r="O12" s="27"/>
-      <c r="P12" s="27"/>
-      <c r="Q12" s="27"/>
-      <c r="R12" s="27"/>
-      <c r="S12" s="27"/>
-      <c r="T12" s="27"/>
-      <c r="U12" s="27"/>
-      <c r="V12" s="27"/>
-      <c r="W12" s="27"/>
-      <c r="X12" s="28"/>
+      <c r="X12" s="17"/>
     </row>
     <row r="13" spans="3:25" x14ac:dyDescent="0.2">
-      <c r="C13" s="24" t="s">
+      <c r="C13" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="D13" s="27"/>
-      <c r="E13" s="27"/>
-      <c r="F13" s="27"/>
-      <c r="G13" s="27"/>
-      <c r="H13" s="27"/>
-      <c r="I13" s="27"/>
-      <c r="J13" s="27"/>
-      <c r="K13" s="27"/>
-      <c r="L13" s="27"/>
-      <c r="M13" s="27"/>
-      <c r="N13" s="27"/>
-      <c r="O13" s="27"/>
-      <c r="P13" s="27"/>
-      <c r="Q13" s="27"/>
-      <c r="R13" s="27"/>
-      <c r="S13" s="27"/>
-      <c r="T13" s="27"/>
-      <c r="U13" s="27"/>
-      <c r="V13" s="27"/>
-      <c r="W13" s="27"/>
-      <c r="X13" s="28"/>
+      <c r="X13" s="17"/>
     </row>
     <row r="14" spans="3:25" x14ac:dyDescent="0.2">
-      <c r="C14" s="29"/>
-      <c r="D14" s="30"/>
-      <c r="E14" s="30"/>
-      <c r="F14" s="30"/>
-      <c r="G14" s="30"/>
-      <c r="H14" s="30"/>
-      <c r="I14" s="30"/>
-      <c r="J14" s="30"/>
-      <c r="K14" s="30"/>
-      <c r="L14" s="30"/>
-      <c r="M14" s="30"/>
-      <c r="N14" s="30"/>
-      <c r="O14" s="30"/>
-      <c r="P14" s="30"/>
-      <c r="Q14" s="30"/>
-      <c r="R14" s="30"/>
-      <c r="S14" s="30"/>
-      <c r="T14" s="30"/>
-      <c r="U14" s="30"/>
-      <c r="V14" s="30"/>
-      <c r="W14" s="30"/>
-      <c r="X14" s="31"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="19"/>
+      <c r="I14" s="19"/>
+      <c r="J14" s="19"/>
+      <c r="K14" s="19"/>
+      <c r="L14" s="19"/>
+      <c r="M14" s="19"/>
+      <c r="N14" s="19"/>
+      <c r="O14" s="19"/>
+      <c r="P14" s="19"/>
+      <c r="Q14" s="19"/>
+      <c r="R14" s="19"/>
+      <c r="S14" s="19"/>
+      <c r="T14" s="19"/>
+      <c r="U14" s="19"/>
+      <c r="V14" s="19"/>
+      <c r="W14" s="19"/>
+      <c r="X14" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="F2:N2"/>
-    <mergeCell ref="O2:R2"/>
-    <mergeCell ref="O3:P3"/>
-    <mergeCell ref="Q3:R3"/>
-    <mergeCell ref="U3:U4"/>
-    <mergeCell ref="V3:V4"/>
-    <mergeCell ref="W3:W4"/>
-    <mergeCell ref="X3:X4"/>
-    <mergeCell ref="S3:S4"/>
-    <mergeCell ref="T3:T4"/>
     <mergeCell ref="C1:X1"/>
     <mergeCell ref="C2:E2"/>
     <mergeCell ref="S2:V2"/>
@@ -1894,6 +1838,16 @@
     <mergeCell ref="L3:L4"/>
     <mergeCell ref="M3:M4"/>
     <mergeCell ref="N3:N4"/>
+    <mergeCell ref="V3:V4"/>
+    <mergeCell ref="W3:W4"/>
+    <mergeCell ref="X3:X4"/>
+    <mergeCell ref="S3:S4"/>
+    <mergeCell ref="T3:T4"/>
+    <mergeCell ref="F2:N2"/>
+    <mergeCell ref="O2:R2"/>
+    <mergeCell ref="O3:P3"/>
+    <mergeCell ref="Q3:R3"/>
+    <mergeCell ref="U3:U4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1904,458 +1858,396 @@
   <dimension ref="C1:W12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="9.33203125" style="34"/>
-    <col min="3" max="3" width="23.33203125" style="34" customWidth="1"/>
-    <col min="4" max="4" width="18.6640625" style="34" customWidth="1"/>
-    <col min="5" max="5" width="24.5" style="34" customWidth="1"/>
-    <col min="6" max="6" width="15.1640625" style="34" customWidth="1"/>
-    <col min="7" max="8" width="12.6640625" style="34" customWidth="1"/>
-    <col min="9" max="9" width="19.83203125" style="34" customWidth="1"/>
-    <col min="10" max="10" width="18.6640625" style="34" customWidth="1"/>
-    <col min="11" max="11" width="8" style="34" customWidth="1"/>
-    <col min="12" max="12" width="20" style="34" customWidth="1"/>
-    <col min="13" max="13" width="6.83203125" style="34" customWidth="1"/>
-    <col min="14" max="14" width="12.6640625" style="34" customWidth="1"/>
-    <col min="15" max="15" width="14" style="34" customWidth="1"/>
-    <col min="16" max="16" width="12.6640625" style="34" customWidth="1"/>
-    <col min="17" max="17" width="10.5" style="34" customWidth="1"/>
-    <col min="18" max="18" width="11.5" style="34" customWidth="1"/>
-    <col min="19" max="19" width="28" style="34" customWidth="1"/>
-    <col min="20" max="20" width="23.5" style="34" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="17.33203125" style="34" customWidth="1"/>
-    <col min="22" max="22" width="38.1640625" style="34" customWidth="1"/>
-    <col min="23" max="23" width="75.83203125" style="34" customWidth="1"/>
-    <col min="24" max="16384" width="9.33203125" style="34"/>
+    <col min="1" max="2" width="9.33203125" style="22"/>
+    <col min="3" max="3" width="23.33203125" style="22" customWidth="1"/>
+    <col min="4" max="4" width="18.6640625" style="22" customWidth="1"/>
+    <col min="5" max="5" width="24.5" style="22" customWidth="1"/>
+    <col min="6" max="6" width="15.1640625" style="22" customWidth="1"/>
+    <col min="7" max="8" width="12.6640625" style="22" customWidth="1"/>
+    <col min="9" max="9" width="19.83203125" style="22" customWidth="1"/>
+    <col min="10" max="10" width="18.6640625" style="22" customWidth="1"/>
+    <col min="11" max="11" width="8" style="22" customWidth="1"/>
+    <col min="12" max="12" width="20" style="22" customWidth="1"/>
+    <col min="13" max="13" width="6.83203125" style="22" customWidth="1"/>
+    <col min="14" max="14" width="12.6640625" style="22" customWidth="1"/>
+    <col min="15" max="15" width="14" style="22" customWidth="1"/>
+    <col min="16" max="16" width="12.6640625" style="22" customWidth="1"/>
+    <col min="17" max="17" width="10.5" style="22" customWidth="1"/>
+    <col min="18" max="18" width="11.5" style="22" customWidth="1"/>
+    <col min="19" max="19" width="28" style="22" customWidth="1"/>
+    <col min="20" max="20" width="23.5" style="22" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="17.33203125" style="22" customWidth="1"/>
+    <col min="22" max="22" width="38.1640625" style="22" customWidth="1"/>
+    <col min="23" max="23" width="75.83203125" style="22" customWidth="1"/>
+    <col min="24" max="16384" width="9.33203125" style="22"/>
   </cols>
   <sheetData>
     <row r="1" spans="3:23" ht="35.450000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C1" s="73" t="s">
+      <c r="C1" s="61" t="s">
         <v>79</v>
       </c>
-      <c r="D1" s="74"/>
-      <c r="E1" s="74"/>
-      <c r="F1" s="74"/>
-      <c r="G1" s="74"/>
-      <c r="H1" s="74"/>
-      <c r="I1" s="74"/>
-      <c r="J1" s="74"/>
-      <c r="K1" s="74"/>
-      <c r="L1" s="74"/>
-      <c r="M1" s="74"/>
-      <c r="N1" s="74"/>
-      <c r="O1" s="74"/>
-      <c r="P1" s="74"/>
-      <c r="Q1" s="74"/>
-      <c r="R1" s="74"/>
-      <c r="S1" s="74"/>
-      <c r="T1" s="74"/>
-      <c r="U1" s="74"/>
-      <c r="V1" s="75"/>
-      <c r="W1" s="33"/>
+      <c r="D1" s="62"/>
+      <c r="E1" s="62"/>
+      <c r="F1" s="62"/>
+      <c r="G1" s="62"/>
+      <c r="H1" s="62"/>
+      <c r="I1" s="62"/>
+      <c r="J1" s="62"/>
+      <c r="K1" s="62"/>
+      <c r="L1" s="62"/>
+      <c r="M1" s="62"/>
+      <c r="N1" s="62"/>
+      <c r="O1" s="62"/>
+      <c r="P1" s="62"/>
+      <c r="Q1" s="62"/>
+      <c r="R1" s="62"/>
+      <c r="S1" s="62"/>
+      <c r="T1" s="62"/>
+      <c r="U1" s="62"/>
+      <c r="V1" s="63"/>
+      <c r="W1" s="21"/>
     </row>
     <row r="2" spans="3:23" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C2" s="38" t="s">
+      <c r="C2" s="55" t="s">
         <v>56</v>
       </c>
-      <c r="D2" s="38" t="s">
+      <c r="D2" s="55" t="s">
         <v>57</v>
       </c>
-      <c r="E2" s="38" t="s">
+      <c r="E2" s="55" t="s">
         <v>58</v>
       </c>
-      <c r="F2" s="38" t="s">
+      <c r="F2" s="55" t="s">
         <v>59</v>
       </c>
-      <c r="G2" s="41" t="s">
+      <c r="G2" s="64" t="s">
         <v>60</v>
       </c>
-      <c r="H2" s="43"/>
-      <c r="I2" s="38" t="s">
+      <c r="H2" s="60"/>
+      <c r="I2" s="55" t="s">
         <v>61</v>
       </c>
-      <c r="J2" s="37" t="s">
+      <c r="J2" s="57" t="s">
         <v>68</v>
       </c>
-      <c r="K2" s="44" t="s">
+      <c r="K2" s="65" t="s">
         <v>62</v>
       </c>
-      <c r="L2" s="37" t="s">
+      <c r="L2" s="57" t="s">
         <v>87</v>
       </c>
-      <c r="M2" s="42" t="s">
+      <c r="M2" s="59" t="s">
         <v>69</v>
       </c>
-      <c r="N2" s="42"/>
-      <c r="O2" s="43"/>
-      <c r="P2" s="38" t="s">
+      <c r="N2" s="59"/>
+      <c r="O2" s="60"/>
+      <c r="P2" s="55" t="s">
         <v>63</v>
       </c>
-      <c r="Q2" s="37" t="s">
+      <c r="Q2" s="57" t="s">
         <v>48</v>
       </c>
-      <c r="R2" s="37" t="s">
+      <c r="R2" s="57" t="s">
         <v>49</v>
       </c>
-      <c r="S2" s="38" t="s">
+      <c r="S2" s="55" t="s">
         <v>64</v>
       </c>
-      <c r="T2" s="37" t="s">
+      <c r="T2" s="57" t="s">
         <v>83</v>
       </c>
-      <c r="U2" s="38" t="s">
+      <c r="U2" s="55" t="s">
         <v>65</v>
       </c>
-      <c r="V2" s="37" t="s">
+      <c r="V2" s="57" t="s">
         <v>8</v>
       </c>
-      <c r="W2" s="35"/>
+      <c r="W2" s="23"/>
     </row>
     <row r="3" spans="3:23" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="40"/>
-      <c r="G3" s="45" t="s">
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="H3" s="45" t="s">
+      <c r="H3" s="25" t="s">
         <v>67</v>
       </c>
-      <c r="I3" s="40"/>
-      <c r="J3" s="40"/>
-      <c r="K3" s="46"/>
-      <c r="L3" s="40"/>
-      <c r="M3" s="54" t="s">
+      <c r="I3" s="56"/>
+      <c r="J3" s="56"/>
+      <c r="K3" s="66"/>
+      <c r="L3" s="56"/>
+      <c r="M3" s="33" t="s">
         <v>29</v>
       </c>
-      <c r="N3" s="47" t="s">
+      <c r="N3" s="26" t="s">
         <v>50</v>
       </c>
-      <c r="O3" s="47" t="s">
+      <c r="O3" s="26" t="s">
         <v>51</v>
       </c>
-      <c r="P3" s="40"/>
-      <c r="Q3" s="39"/>
-      <c r="R3" s="39"/>
-      <c r="S3" s="40"/>
-      <c r="T3" s="39"/>
-      <c r="U3" s="40"/>
-      <c r="V3" s="39"/>
-      <c r="W3" s="35"/>
+      <c r="P3" s="56"/>
+      <c r="Q3" s="58"/>
+      <c r="R3" s="58"/>
+      <c r="S3" s="79"/>
+      <c r="T3" s="80"/>
+      <c r="U3" s="79"/>
+      <c r="V3" s="80"/>
+      <c r="W3" s="23"/>
     </row>
     <row r="4" spans="3:23" x14ac:dyDescent="0.25">
-      <c r="C4" s="76" t="s">
+      <c r="C4" s="49" t="s">
         <v>52</v>
       </c>
-      <c r="D4" s="82">
+      <c r="D4" s="53">
         <v>35.417999999999999</v>
       </c>
-      <c r="E4" s="49">
+      <c r="E4" s="28">
         <v>27.395</v>
       </c>
-      <c r="F4" s="51">
+      <c r="F4" s="30">
         <v>95</v>
       </c>
-      <c r="G4" s="51">
+      <c r="G4" s="30">
         <v>80</v>
       </c>
-      <c r="H4" s="51">
+      <c r="H4" s="30">
         <v>67</v>
       </c>
-      <c r="I4" s="50">
+      <c r="I4" s="29">
         <v>1265</v>
       </c>
-      <c r="J4" s="49">
+      <c r="J4" s="28">
         <v>0.5</v>
       </c>
-      <c r="K4" s="53">
+      <c r="K4" s="32">
         <v>0.75</v>
       </c>
-      <c r="L4" s="51" t="s">
+      <c r="L4" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="M4" s="77" t="s">
+      <c r="M4" s="50" t="s">
         <v>53</v>
       </c>
-      <c r="N4" s="51">
+      <c r="N4" s="30">
         <v>45</v>
       </c>
-      <c r="O4" s="48">
+      <c r="O4" s="27">
         <v>36.450000000000003</v>
       </c>
-      <c r="P4" s="76" t="s">
+      <c r="P4" s="49" t="s">
         <v>54</v>
       </c>
-      <c r="Q4" s="49">
+      <c r="Q4" s="28">
         <v>19.899999999999999</v>
       </c>
-      <c r="R4" s="49">
+      <c r="R4" s="77">
         <v>30</v>
       </c>
-      <c r="S4" s="78" t="s">
+      <c r="S4" s="81" t="s">
         <v>80</v>
       </c>
-      <c r="T4" s="78" t="s">
+      <c r="T4" s="81" t="s">
         <v>84</v>
       </c>
-      <c r="U4" s="51" t="s">
+      <c r="U4" s="82" t="s">
         <v>39</v>
       </c>
-      <c r="V4" s="45" t="s">
+      <c r="V4" s="83" t="s">
         <v>86</v>
       </c>
-      <c r="W4" s="35"/>
+      <c r="W4" s="23"/>
     </row>
     <row r="5" spans="3:23" x14ac:dyDescent="0.25">
-      <c r="C5" s="79" t="s">
+      <c r="C5" s="51" t="s">
         <v>55</v>
       </c>
-      <c r="D5" s="83">
+      <c r="D5" s="54">
         <v>46.220999999999997</v>
       </c>
-      <c r="E5" s="56">
+      <c r="E5" s="35">
         <v>36.290999999999997</v>
       </c>
-      <c r="F5" s="59">
+      <c r="F5" s="38">
         <v>95</v>
       </c>
-      <c r="G5" s="59">
+      <c r="G5" s="38">
         <v>80</v>
       </c>
-      <c r="H5" s="59">
+      <c r="H5" s="38">
         <v>67</v>
       </c>
-      <c r="I5" s="57">
+      <c r="I5" s="36">
         <v>1660</v>
       </c>
-      <c r="J5" s="56">
+      <c r="J5" s="35">
         <v>0.5</v>
       </c>
-      <c r="K5" s="58">
+      <c r="K5" s="37">
         <v>1.2</v>
       </c>
-      <c r="L5" s="59" t="s">
+      <c r="L5" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="M5" s="80" t="s">
+      <c r="M5" s="52" t="s">
         <v>53</v>
       </c>
-      <c r="N5" s="59">
+      <c r="N5" s="38">
         <v>115</v>
       </c>
-      <c r="O5" s="55">
+      <c r="O5" s="34">
         <v>93.15</v>
       </c>
-      <c r="P5" s="79" t="s">
+      <c r="P5" s="51" t="s">
         <v>82</v>
       </c>
-      <c r="Q5" s="56">
+      <c r="Q5" s="35">
         <v>10.6</v>
       </c>
-      <c r="R5" s="56">
+      <c r="R5" s="78">
         <v>15</v>
       </c>
-      <c r="S5" s="79" t="s">
+      <c r="S5" s="84" t="s">
         <v>81</v>
       </c>
       <c r="T5" s="81" t="s">
         <v>85</v>
       </c>
-      <c r="U5" s="59" t="s">
+      <c r="U5" s="82" t="s">
         <v>39</v>
       </c>
-      <c r="V5" s="45" t="s">
+      <c r="V5" s="83" t="s">
         <v>86</v>
       </c>
-      <c r="W5" s="35"/>
+      <c r="W5" s="23"/>
     </row>
     <row r="6" spans="3:23" x14ac:dyDescent="0.25">
-      <c r="C6" s="21" t="s">
+      <c r="C6" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="D6" s="64"/>
-      <c r="E6" s="64"/>
-      <c r="F6" s="64"/>
-      <c r="G6" s="64"/>
-      <c r="H6" s="64"/>
-      <c r="I6" s="64"/>
-      <c r="J6" s="64"/>
-      <c r="K6" s="64"/>
-      <c r="L6" s="64"/>
-      <c r="M6" s="65"/>
-      <c r="N6" s="65" t="s">
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="40"/>
+      <c r="K6" s="40"/>
+      <c r="L6" s="40"/>
+      <c r="M6" s="41"/>
+      <c r="N6" s="41" t="s">
         <v>76</v>
       </c>
-      <c r="O6" s="66"/>
-      <c r="P6" s="66"/>
-      <c r="Q6" s="66"/>
-      <c r="R6" s="66"/>
-      <c r="S6" s="66"/>
-      <c r="T6" s="66"/>
-      <c r="U6" s="66"/>
-      <c r="V6" s="67"/>
-      <c r="W6" s="52"/>
+      <c r="O6" s="42"/>
+      <c r="P6" s="42"/>
+      <c r="Q6" s="42"/>
+      <c r="R6" s="42"/>
+      <c r="S6" s="42"/>
+      <c r="T6" s="42"/>
+      <c r="U6" s="42"/>
+      <c r="V6" s="43"/>
+      <c r="W6" s="31"/>
     </row>
     <row r="7" spans="3:23" x14ac:dyDescent="0.2">
-      <c r="C7" s="24" t="s">
+      <c r="C7" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="D7" s="60"/>
-      <c r="E7" s="60"/>
-      <c r="F7" s="60"/>
-      <c r="G7" s="60"/>
-      <c r="H7" s="60"/>
-      <c r="I7" s="60"/>
-      <c r="J7" s="60"/>
-      <c r="K7" s="60"/>
-      <c r="L7" s="61"/>
-      <c r="M7" s="60"/>
-      <c r="N7" s="62" t="s">
+      <c r="D7" s="31"/>
+      <c r="E7" s="31"/>
+      <c r="F7" s="31"/>
+      <c r="G7" s="31"/>
+      <c r="H7" s="31"/>
+      <c r="I7" s="31"/>
+      <c r="J7" s="31"/>
+      <c r="K7" s="31"/>
+      <c r="L7" s="24"/>
+      <c r="M7" s="31"/>
+      <c r="N7" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="O7" s="60"/>
-      <c r="P7" s="60"/>
-      <c r="Q7" s="60"/>
-      <c r="R7" s="60"/>
-      <c r="S7" s="60"/>
-      <c r="T7" s="60"/>
-      <c r="U7" s="60"/>
-      <c r="V7" s="68"/>
-      <c r="W7" s="52"/>
+      <c r="O7" s="31"/>
+      <c r="P7" s="31"/>
+      <c r="Q7" s="31"/>
+      <c r="R7" s="31"/>
+      <c r="S7" s="31"/>
+      <c r="T7" s="31"/>
+      <c r="U7" s="31"/>
+      <c r="V7" s="44"/>
+      <c r="W7" s="31"/>
     </row>
     <row r="8" spans="3:23" x14ac:dyDescent="0.2">
-      <c r="C8" s="24" t="s">
+      <c r="C8" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="D8" s="60"/>
-      <c r="E8" s="60"/>
-      <c r="F8" s="60"/>
-      <c r="G8" s="60"/>
-      <c r="H8" s="60"/>
-      <c r="I8" s="60"/>
-      <c r="J8" s="60"/>
-      <c r="K8" s="60"/>
-      <c r="L8" s="61"/>
-      <c r="M8" s="61"/>
-      <c r="N8" s="63" t="s">
+      <c r="D8" s="31"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="31"/>
+      <c r="G8" s="31"/>
+      <c r="H8" s="31"/>
+      <c r="I8" s="31"/>
+      <c r="J8" s="31"/>
+      <c r="K8" s="31"/>
+      <c r="L8" s="24"/>
+      <c r="M8" s="24"/>
+      <c r="N8" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="O8" s="61"/>
-      <c r="P8" s="61"/>
-      <c r="Q8" s="61"/>
-      <c r="R8" s="61"/>
-      <c r="S8" s="61"/>
-      <c r="T8" s="61"/>
-      <c r="U8" s="61"/>
-      <c r="V8" s="69"/>
-      <c r="W8" s="36"/>
+      <c r="O8" s="24"/>
+      <c r="P8" s="24"/>
+      <c r="Q8" s="24"/>
+      <c r="R8" s="24"/>
+      <c r="S8" s="24"/>
+      <c r="T8" s="24"/>
+      <c r="U8" s="24"/>
+      <c r="V8" s="45"/>
+      <c r="W8" s="24"/>
     </row>
     <row r="9" spans="3:23" x14ac:dyDescent="0.2">
-      <c r="C9" s="24" t="s">
+      <c r="C9" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="D9" s="63"/>
-      <c r="E9" s="63"/>
-      <c r="F9" s="63"/>
-      <c r="G9" s="63"/>
-      <c r="H9" s="63"/>
-      <c r="I9" s="63"/>
-      <c r="J9" s="63"/>
-      <c r="K9" s="63"/>
-      <c r="L9" s="63"/>
-      <c r="M9" s="63"/>
-      <c r="N9" s="63"/>
-      <c r="O9" s="63"/>
-      <c r="P9" s="63"/>
-      <c r="Q9" s="63"/>
-      <c r="R9" s="63"/>
-      <c r="S9" s="63"/>
-      <c r="T9" s="63"/>
-      <c r="U9" s="63"/>
-      <c r="V9" s="70"/>
+      <c r="V9" s="46"/>
     </row>
     <row r="10" spans="3:23" x14ac:dyDescent="0.2">
-      <c r="C10" s="24" t="s">
+      <c r="C10" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="D10" s="63"/>
-      <c r="E10" s="63"/>
-      <c r="F10" s="63"/>
-      <c r="G10" s="63"/>
-      <c r="H10" s="63"/>
-      <c r="I10" s="63"/>
-      <c r="J10" s="63"/>
-      <c r="K10" s="63"/>
-      <c r="L10" s="63"/>
-      <c r="M10" s="63"/>
-      <c r="N10" s="63"/>
-      <c r="O10" s="63"/>
-      <c r="P10" s="63"/>
-      <c r="Q10" s="63"/>
-      <c r="R10" s="63"/>
-      <c r="S10" s="63"/>
-      <c r="T10" s="63"/>
-      <c r="U10" s="63"/>
-      <c r="V10" s="70"/>
+      <c r="V10" s="46"/>
     </row>
     <row r="11" spans="3:23" x14ac:dyDescent="0.2">
-      <c r="C11" s="24" t="s">
+      <c r="C11" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="D11" s="63"/>
-      <c r="E11" s="63"/>
-      <c r="F11" s="63"/>
-      <c r="G11" s="63"/>
-      <c r="H11" s="63"/>
-      <c r="I11" s="63"/>
-      <c r="J11" s="63"/>
-      <c r="K11" s="63"/>
-      <c r="L11" s="63"/>
-      <c r="M11" s="63"/>
-      <c r="N11" s="63"/>
-      <c r="O11" s="63"/>
-      <c r="P11" s="63"/>
-      <c r="Q11" s="63"/>
-      <c r="R11" s="63"/>
-      <c r="S11" s="63"/>
-      <c r="T11" s="63"/>
-      <c r="U11" s="63"/>
-      <c r="V11" s="70"/>
+      <c r="V11" s="46"/>
     </row>
     <row r="12" spans="3:23" x14ac:dyDescent="0.2">
-      <c r="C12" s="29" t="s">
+      <c r="C12" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="D12" s="71"/>
-      <c r="E12" s="71"/>
-      <c r="F12" s="71"/>
-      <c r="G12" s="71"/>
-      <c r="H12" s="71"/>
-      <c r="I12" s="71"/>
-      <c r="J12" s="71"/>
-      <c r="K12" s="71"/>
-      <c r="L12" s="71"/>
-      <c r="M12" s="71"/>
-      <c r="N12" s="71"/>
-      <c r="O12" s="71"/>
-      <c r="P12" s="71"/>
-      <c r="Q12" s="71"/>
-      <c r="R12" s="71"/>
-      <c r="S12" s="71"/>
-      <c r="T12" s="71"/>
-      <c r="U12" s="71"/>
-      <c r="V12" s="72"/>
+      <c r="D12" s="47"/>
+      <c r="E12" s="47"/>
+      <c r="F12" s="47"/>
+      <c r="G12" s="47"/>
+      <c r="H12" s="47"/>
+      <c r="I12" s="47"/>
+      <c r="J12" s="47"/>
+      <c r="K12" s="47"/>
+      <c r="L12" s="47"/>
+      <c r="M12" s="47"/>
+      <c r="N12" s="47"/>
+      <c r="O12" s="47"/>
+      <c r="P12" s="47"/>
+      <c r="Q12" s="47"/>
+      <c r="R12" s="47"/>
+      <c r="S12" s="47"/>
+      <c r="T12" s="47"/>
+      <c r="U12" s="47"/>
+      <c r="V12" s="48"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="U2:U3"/>
-    <mergeCell ref="V2:V3"/>
-    <mergeCell ref="M2:O2"/>
-    <mergeCell ref="P2:P3"/>
-    <mergeCell ref="Q2:Q3"/>
-    <mergeCell ref="R2:R3"/>
-    <mergeCell ref="S2:S3"/>
-    <mergeCell ref="T2:T3"/>
     <mergeCell ref="C1:V1"/>
     <mergeCell ref="C2:C3"/>
     <mergeCell ref="D2:D3"/>
@@ -2366,6 +2258,14 @@
     <mergeCell ref="J2:J3"/>
     <mergeCell ref="K2:K3"/>
     <mergeCell ref="L2:L3"/>
+    <mergeCell ref="U2:U3"/>
+    <mergeCell ref="V2:V3"/>
+    <mergeCell ref="M2:O2"/>
+    <mergeCell ref="P2:P3"/>
+    <mergeCell ref="Q2:Q3"/>
+    <mergeCell ref="R2:R3"/>
+    <mergeCell ref="S2:S3"/>
+    <mergeCell ref="T2:T3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
